--- a/accountant-skill/data/input/ledgers/fixed_assets_ledger.xlsx
+++ b/accountant-skill/data/input/ledgers/fixed_assets_ledger.xlsx
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
